--- a/examples/reelmate-cases-excel/context.xlsx
+++ b/examples/reelmate-cases-excel/context.xlsx
@@ -10,7 +10,6 @@
     <sheet name="浏览器配置" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="WEB页面元素" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="通用配置" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="数据库配置" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,6 +452,8 @@
           <t>chromium</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>{"browserName": "chromium"}</t>
@@ -593,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[class*="avatar"], [class*="user"]</t>
+          <t>[class*="avatar"], [class*="user"], [class*="nickname"]</t>
         </is>
       </c>
     </row>
@@ -690,58 +691,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>别名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>服务器IP</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>端口号</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>用户名</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>密码</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>数据库名称</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>